--- a/DemoBlazePOM/src/test/resources/Files.xlsx
+++ b/DemoBlazePOM/src/test/resources/Files.xlsx
@@ -3,21 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sowndariya\Desktop\Expleo\TestNG\DemoBlaze Website\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7DDB8E-A6E0-4636-B683-B25DA529F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{604AF5C6-6664-41E5-9327-1E932DCCBB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>UserName</t>
   </si>
@@ -51,6 +47,12 @@
   </si>
   <si>
     <t>Sow@911</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
   </si>
 </sst>
 </file>
@@ -404,6 +406,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -415,15 +420,15 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{AD9B642E-F606-4AA7-92E6-4040DF3F88D5}"/>
+    <hyperlink ref="B2" r:id="rId1" display="Sow@911!" xr:uid="{AD9B642E-F606-4AA7-92E6-4040DF3F88D5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
